--- a/Annotation_Main/Main2/Main2_consolidation.xlsx
+++ b/Annotation_Main/Main2/Main2_consolidation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/katja/Dropbox/Doktorat/ParlaMint/Sentiment_annotation-speeches/Annotation_Main/Main2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21FE20E5-07BD-7940-A599-D8A7932DCBD3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71EB72D8-BB9B-8749-B15E-FEB85B348BA9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16220" xr2:uid="{C17540B4-08CA-9F42-988F-D06AE64B845A}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Main2_consolidation" localSheetId="0">Sheet1!$A$1:$J$201</definedName>
+    <definedName name="Main2_consolidation" localSheetId="0">Sheet1!$A$1:$L$201</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1309" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1711" uniqueCount="566">
   <si>
     <t>ID</t>
   </si>
@@ -1741,14 +1741,38 @@
   </si>
   <si>
     <t>If first part is read as sarcastic it could also be Negative.</t>
+  </si>
+  <si>
+    <t>sent_tamara</t>
+  </si>
+  <si>
+    <t>sent_katja</t>
+  </si>
+  <si>
+    <t>Neutral</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1782,7 +1806,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1791,6 +1815,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2109,7 +2136,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9C7C9A9-21B6-6A47-9274-33B14FEDB1AE}">
-  <dimension ref="A1:J201"/>
+  <dimension ref="A1:L201"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="41.1640625" bestFit="1" customWidth="1"/>
@@ -2118,11 +2145,12 @@
     <col min="5" max="6" width="80.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.33203125" customWidth="1"/>
     <col min="8" max="8" width="5.1640625" customWidth="1"/>
-    <col min="9" max="9" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="10.83203125" style="4"/>
+    <col min="11" max="11" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2147,14 +2175,20 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="5" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -2170,14 +2204,20 @@
       <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I2" t="b">
-        <v>1</v>
-      </c>
-      <c r="J2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="I2" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="68" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -2193,14 +2233,20 @@
       <c r="E3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="I3" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -2216,14 +2262,20 @@
       <c r="E4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I4" t="b">
-        <v>1</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="I4" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -2239,14 +2291,20 @@
       <c r="E5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I5" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -2262,14 +2320,20 @@
       <c r="E6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="221" x14ac:dyDescent="0.2">
+      <c r="I6" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="221" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -2291,14 +2355,20 @@
       <c r="H7" t="s">
         <v>30</v>
       </c>
-      <c r="I7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>31</v>
       </c>
@@ -2314,14 +2384,20 @@
       <c r="E8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I8" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="356" x14ac:dyDescent="0.2">
+      <c r="I8" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="356" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>33</v>
       </c>
@@ -2340,14 +2416,20 @@
       <c r="F9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I9" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="I9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -2369,14 +2451,20 @@
       <c r="H10" t="s">
         <v>30</v>
       </c>
-      <c r="I10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J10" t="s">
+      <c r="I10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -2398,14 +2486,20 @@
       <c r="G11" t="s">
         <v>30</v>
       </c>
-      <c r="I11" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" t="s">
+      <c r="I11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="388" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" ht="388" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -2430,14 +2524,20 @@
       <c r="H12" t="s">
         <v>30</v>
       </c>
-      <c r="I12" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="272" x14ac:dyDescent="0.2">
+      <c r="I12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="272" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>50</v>
       </c>
@@ -2453,14 +2553,20 @@
       <c r="E13" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I13" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I13" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>54</v>
       </c>
@@ -2476,14 +2582,20 @@
       <c r="E14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I14" t="b">
-        <v>1</v>
-      </c>
-      <c r="J14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I14" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>56</v>
       </c>
@@ -2499,14 +2611,20 @@
       <c r="E15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I15" t="b">
-        <v>1</v>
-      </c>
-      <c r="J15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I15" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K15" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>58</v>
       </c>
@@ -2525,14 +2643,20 @@
       <c r="F16" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I16" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="356" x14ac:dyDescent="0.2">
+      <c r="I16" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="356" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>62</v>
       </c>
@@ -2548,14 +2672,20 @@
       <c r="E17" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="289" x14ac:dyDescent="0.2">
+      <c r="I17" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="289" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>64</v>
       </c>
@@ -2574,14 +2704,20 @@
       <c r="F18" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="I18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J18" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="I18" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="68" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>68</v>
       </c>
@@ -2597,14 +2733,20 @@
       <c r="E19" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I19" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" t="s">
+      <c r="I19" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>70</v>
       </c>
@@ -2620,14 +2762,20 @@
       <c r="E20" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I20" t="b">
-        <v>1</v>
-      </c>
-      <c r="J20" t="s">
+      <c r="I20" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K20" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>72</v>
       </c>
@@ -2646,14 +2794,20 @@
       <c r="F21" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="I21" t="b">
-        <v>0</v>
-      </c>
-      <c r="J21" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I21" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>76</v>
       </c>
@@ -2678,14 +2832,20 @@
       <c r="H22" t="s">
         <v>30</v>
       </c>
-      <c r="I22" t="b">
-        <v>0</v>
-      </c>
-      <c r="J22" t="s">
+      <c r="I22" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>81</v>
       </c>
@@ -2701,14 +2861,20 @@
       <c r="E23" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I23" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="I23" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K23" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="68" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>83</v>
       </c>
@@ -2724,14 +2890,20 @@
       <c r="E24" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I24" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K24" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>85</v>
       </c>
@@ -2747,14 +2919,20 @@
       <c r="E25" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I25" t="b">
-        <v>0</v>
-      </c>
-      <c r="J25" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="I25" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="68" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>88</v>
       </c>
@@ -2770,14 +2948,20 @@
       <c r="E26" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J26" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="289" x14ac:dyDescent="0.2">
+      <c r="I26" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K26" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="289" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>90</v>
       </c>
@@ -2793,14 +2977,20 @@
       <c r="E27" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I27" t="b">
-        <v>0</v>
-      </c>
-      <c r="J27" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="340" x14ac:dyDescent="0.2">
+      <c r="I27" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="340" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>92</v>
       </c>
@@ -2822,14 +3012,20 @@
       <c r="H28" t="s">
         <v>30</v>
       </c>
-      <c r="I28" t="b">
-        <v>0</v>
-      </c>
-      <c r="J28" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I28" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>96</v>
       </c>
@@ -2845,14 +3041,20 @@
       <c r="E29" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I29" t="b">
-        <v>1</v>
-      </c>
-      <c r="J29" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="I29" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K29" t="b">
+        <v>1</v>
+      </c>
+      <c r="L29" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>98</v>
       </c>
@@ -2868,14 +3070,20 @@
       <c r="E30" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I30" t="b">
-        <v>1</v>
-      </c>
-      <c r="J30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I30" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K30" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>100</v>
       </c>
@@ -2894,14 +3102,20 @@
       <c r="F31" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="I31" t="b">
-        <v>0</v>
-      </c>
-      <c r="J31" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="255" x14ac:dyDescent="0.2">
+      <c r="I31" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="255" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>104</v>
       </c>
@@ -2917,14 +3131,20 @@
       <c r="E32" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I32" t="b">
-        <v>1</v>
-      </c>
-      <c r="J32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I32" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>106</v>
       </c>
@@ -2940,14 +3160,20 @@
       <c r="E33" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I33" t="b">
-        <v>0</v>
-      </c>
-      <c r="J33" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I33" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>109</v>
       </c>
@@ -2966,14 +3192,20 @@
       <c r="F34" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="I34" t="b">
-        <v>0</v>
-      </c>
-      <c r="J34" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="289" x14ac:dyDescent="0.2">
+      <c r="I34" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="289" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>113</v>
       </c>
@@ -2992,14 +3224,20 @@
       <c r="F35" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="I35" t="b">
-        <v>0</v>
-      </c>
-      <c r="J35" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="I35" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>117</v>
       </c>
@@ -3018,14 +3256,20 @@
       <c r="F36" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="I36" t="b">
-        <v>0</v>
-      </c>
-      <c r="J36" t="s">
+      <c r="I36" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>121</v>
       </c>
@@ -3041,14 +3285,20 @@
       <c r="E37" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I37" t="b">
-        <v>1</v>
-      </c>
-      <c r="J37" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I37" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K37" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>123</v>
       </c>
@@ -3064,14 +3314,20 @@
       <c r="E38" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I38" t="b">
-        <v>1</v>
-      </c>
-      <c r="J38" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="I38" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J38" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K38" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>125</v>
       </c>
@@ -3093,14 +3349,20 @@
       <c r="H39" t="s">
         <v>30</v>
       </c>
-      <c r="I39" t="b">
-        <v>0</v>
-      </c>
-      <c r="J39" t="s">
+      <c r="I39" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K39" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>129</v>
       </c>
@@ -3116,14 +3378,20 @@
       <c r="E40" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I40" t="b">
-        <v>1</v>
-      </c>
-      <c r="J40" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I40" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K40" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>131</v>
       </c>
@@ -3139,14 +3407,20 @@
       <c r="E41" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I41" t="b">
-        <v>1</v>
-      </c>
-      <c r="J41" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I41" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K41" t="b">
+        <v>1</v>
+      </c>
+      <c r="L41" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>133</v>
       </c>
@@ -3162,14 +3436,20 @@
       <c r="E42" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I42" t="b">
-        <v>1</v>
-      </c>
-      <c r="J42" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="170" x14ac:dyDescent="0.2">
+      <c r="I42" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K42" t="b">
+        <v>1</v>
+      </c>
+      <c r="L42" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="170" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>135</v>
       </c>
@@ -3185,14 +3465,20 @@
       <c r="E43" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="I43" t="b">
-        <v>0</v>
-      </c>
-      <c r="J43" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="I43" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K43" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>138</v>
       </c>
@@ -3208,14 +3494,20 @@
       <c r="E44" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I44" t="b">
-        <v>1</v>
-      </c>
-      <c r="J44" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I44" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J44" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K44" t="b">
+        <v>1</v>
+      </c>
+      <c r="L44" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>140</v>
       </c>
@@ -3231,14 +3523,20 @@
       <c r="E45" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I45" t="b">
-        <v>1</v>
-      </c>
-      <c r="J45" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I45" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K45" t="b">
+        <v>1</v>
+      </c>
+      <c r="L45" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>142</v>
       </c>
@@ -3254,14 +3552,20 @@
       <c r="E46" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I46" t="b">
-        <v>1</v>
-      </c>
-      <c r="J46" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I46" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J46" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K46" t="b">
+        <v>1</v>
+      </c>
+      <c r="L46" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>144</v>
       </c>
@@ -3277,14 +3581,20 @@
       <c r="E47" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="I47" t="b">
-        <v>0</v>
-      </c>
-      <c r="J47" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="170" x14ac:dyDescent="0.2">
+      <c r="I47" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J47" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K47" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="170" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>147</v>
       </c>
@@ -3309,14 +3619,20 @@
       <c r="H48" t="s">
         <v>30</v>
       </c>
-      <c r="I48" t="b">
-        <v>0</v>
-      </c>
-      <c r="J48" t="s">
+      <c r="I48" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J48" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K48" t="b">
+        <v>0</v>
+      </c>
+      <c r="L48" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>151</v>
       </c>
@@ -3332,14 +3648,20 @@
       <c r="E49" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="I49" t="b">
-        <v>0</v>
-      </c>
-      <c r="J49" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="I49" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J49" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K49" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>154</v>
       </c>
@@ -3355,14 +3677,20 @@
       <c r="E50" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I50" t="b">
-        <v>1</v>
-      </c>
-      <c r="J50" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="I50" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J50" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K50" t="b">
+        <v>1</v>
+      </c>
+      <c r="L50" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>156</v>
       </c>
@@ -3378,14 +3706,20 @@
       <c r="E51" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I51" t="b">
-        <v>1</v>
-      </c>
-      <c r="J51" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I51" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J51" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K51" t="b">
+        <v>1</v>
+      </c>
+      <c r="L51" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>158</v>
       </c>
@@ -3401,14 +3735,20 @@
       <c r="E52" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I52" t="b">
-        <v>1</v>
-      </c>
-      <c r="J52" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I52" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K52" t="b">
+        <v>1</v>
+      </c>
+      <c r="L52" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>160</v>
       </c>
@@ -3427,14 +3767,20 @@
       <c r="F53" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="I53" t="b">
-        <v>0</v>
-      </c>
-      <c r="J53" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="323" x14ac:dyDescent="0.2">
+      <c r="I53" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K53" t="b">
+        <v>0</v>
+      </c>
+      <c r="L53" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="323" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>164</v>
       </c>
@@ -3453,14 +3799,20 @@
       <c r="F54" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="I54" t="b">
-        <v>0</v>
-      </c>
-      <c r="J54" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+      <c r="I54" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J54" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K54" t="b">
+        <v>0</v>
+      </c>
+      <c r="L54" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="102" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>168</v>
       </c>
@@ -3476,14 +3828,20 @@
       <c r="E55" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="I55" t="b">
-        <v>0</v>
-      </c>
-      <c r="J55" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="372" x14ac:dyDescent="0.2">
+      <c r="I55" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J55" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K55" t="b">
+        <v>0</v>
+      </c>
+      <c r="L55" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="372" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>171</v>
       </c>
@@ -3502,14 +3860,20 @@
       <c r="F56" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="I56" t="b">
-        <v>0</v>
-      </c>
-      <c r="J56" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I56" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J56" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K56" t="b">
+        <v>0</v>
+      </c>
+      <c r="L56" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>175</v>
       </c>
@@ -3525,14 +3889,20 @@
       <c r="E57" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I57" t="b">
-        <v>1</v>
-      </c>
-      <c r="J57" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I57" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J57" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K57" t="b">
+        <v>1</v>
+      </c>
+      <c r="L57" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>177</v>
       </c>
@@ -3554,14 +3924,20 @@
       <c r="G58" t="s">
         <v>30</v>
       </c>
-      <c r="I58" t="b">
-        <v>0</v>
-      </c>
-      <c r="J58" t="s">
+      <c r="I58" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J58" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K58" t="b">
+        <v>0</v>
+      </c>
+      <c r="L58" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" ht="119" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>181</v>
       </c>
@@ -3577,14 +3953,20 @@
       <c r="E59" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="I59" t="b">
-        <v>0</v>
-      </c>
-      <c r="J59" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="I59" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J59" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K59" t="b">
+        <v>0</v>
+      </c>
+      <c r="L59" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>184</v>
       </c>
@@ -3600,14 +3982,20 @@
       <c r="E60" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I60" t="b">
-        <v>1</v>
-      </c>
-      <c r="J60" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I60" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J60" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K60" t="b">
+        <v>1</v>
+      </c>
+      <c r="L60" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>186</v>
       </c>
@@ -3626,14 +4014,20 @@
       <c r="F61" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="I61" t="b">
-        <v>0</v>
-      </c>
-      <c r="J61" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I61" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J61" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K61" t="b">
+        <v>0</v>
+      </c>
+      <c r="L61" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>189</v>
       </c>
@@ -3649,14 +4043,20 @@
       <c r="E62" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I62" t="b">
-        <v>1</v>
-      </c>
-      <c r="J62" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I62" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J62" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K62" t="b">
+        <v>1</v>
+      </c>
+      <c r="L62" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>191</v>
       </c>
@@ -3672,14 +4072,20 @@
       <c r="E63" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I63" t="b">
-        <v>1</v>
-      </c>
-      <c r="J63" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+      <c r="I63" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J63" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K63" t="b">
+        <v>1</v>
+      </c>
+      <c r="L63" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="119" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>193</v>
       </c>
@@ -3695,14 +4101,20 @@
       <c r="E64" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="I64" t="b">
-        <v>0</v>
-      </c>
-      <c r="J64" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="I64" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J64" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K64" t="b">
+        <v>0</v>
+      </c>
+      <c r="L64" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>196</v>
       </c>
@@ -3724,14 +4136,20 @@
       <c r="H65" t="s">
         <v>30</v>
       </c>
-      <c r="I65" t="b">
-        <v>1</v>
-      </c>
-      <c r="J65" t="s">
+      <c r="I65" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J65" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K65" t="b">
+        <v>1</v>
+      </c>
+      <c r="L65" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>199</v>
       </c>
@@ -3747,14 +4165,20 @@
       <c r="E66" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I66" t="b">
-        <v>1</v>
-      </c>
-      <c r="J66" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I66" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J66" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K66" t="b">
+        <v>1</v>
+      </c>
+      <c r="L66" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>201</v>
       </c>
@@ -3770,14 +4194,20 @@
       <c r="E67" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I67" t="b">
-        <v>1</v>
-      </c>
-      <c r="J67" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I67" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J67" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K67" t="b">
+        <v>1</v>
+      </c>
+      <c r="L67" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>203</v>
       </c>
@@ -3799,14 +4229,20 @@
       <c r="G68" t="s">
         <v>30</v>
       </c>
-      <c r="I68" t="b">
-        <v>0</v>
-      </c>
-      <c r="J68" t="s">
+      <c r="I68" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J68" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K68" t="b">
+        <v>0</v>
+      </c>
+      <c r="L68" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>207</v>
       </c>
@@ -3822,14 +4258,20 @@
       <c r="E69" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I69" t="b">
-        <v>1</v>
-      </c>
-      <c r="J69" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="I69" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J69" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K69" t="b">
+        <v>1</v>
+      </c>
+      <c r="L69" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>209</v>
       </c>
@@ -3845,14 +4287,20 @@
       <c r="E70" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I70" t="b">
-        <v>1</v>
-      </c>
-      <c r="J70" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="I70" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J70" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K70" t="b">
+        <v>1</v>
+      </c>
+      <c r="L70" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>211</v>
       </c>
@@ -3868,14 +4316,20 @@
       <c r="E71" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I71" t="b">
-        <v>1</v>
-      </c>
-      <c r="J71" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I71" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J71" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K71" t="b">
+        <v>1</v>
+      </c>
+      <c r="L71" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>213</v>
       </c>
@@ -3894,14 +4348,20 @@
       <c r="G72" t="s">
         <v>30</v>
       </c>
-      <c r="I72" t="b">
-        <v>0</v>
-      </c>
-      <c r="J72" t="s">
+      <c r="I72" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J72" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K72" t="b">
+        <v>0</v>
+      </c>
+      <c r="L72" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>216</v>
       </c>
@@ -3920,14 +4380,20 @@
       <c r="G73" t="s">
         <v>30</v>
       </c>
-      <c r="I73" t="b">
-        <v>0</v>
-      </c>
-      <c r="J73" t="s">
+      <c r="I73" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J73" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K73" t="b">
+        <v>0</v>
+      </c>
+      <c r="L73" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>219</v>
       </c>
@@ -3943,14 +4409,20 @@
       <c r="F74" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="I74" t="b">
-        <v>0</v>
-      </c>
-      <c r="J74" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I74" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J74" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K74" t="b">
+        <v>0</v>
+      </c>
+      <c r="L74" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>222</v>
       </c>
@@ -3969,14 +4441,20 @@
       <c r="F75" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="I75" t="b">
-        <v>0</v>
-      </c>
-      <c r="J75" t="s">
+      <c r="I75" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J75" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K75" t="b">
+        <v>0</v>
+      </c>
+      <c r="L75" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="136" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" ht="136" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>226</v>
       </c>
@@ -3992,14 +4470,20 @@
       <c r="E76" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I76" t="b">
-        <v>1</v>
-      </c>
-      <c r="J76" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" ht="272" x14ac:dyDescent="0.2">
+      <c r="I76" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J76" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K76" t="b">
+        <v>1</v>
+      </c>
+      <c r="L76" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="272" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>228</v>
       </c>
@@ -4018,14 +4502,20 @@
       <c r="F77" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="I77" t="b">
-        <v>0</v>
-      </c>
-      <c r="J77" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I77" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J77" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K77" t="b">
+        <v>0</v>
+      </c>
+      <c r="L77" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>231</v>
       </c>
@@ -4041,14 +4531,20 @@
       <c r="E78" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I78" t="b">
-        <v>1</v>
-      </c>
-      <c r="J78" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="I78" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J78" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K78" t="b">
+        <v>1</v>
+      </c>
+      <c r="L78" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>233</v>
       </c>
@@ -4064,14 +4560,20 @@
       <c r="E79" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I79" t="b">
-        <v>1</v>
-      </c>
-      <c r="J79" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I79" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J79" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K79" t="b">
+        <v>1</v>
+      </c>
+      <c r="L79" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>235</v>
       </c>
@@ -4087,14 +4589,20 @@
       <c r="E80" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I80" t="b">
-        <v>1</v>
-      </c>
-      <c r="J80" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" ht="306" x14ac:dyDescent="0.2">
+      <c r="I80" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J80" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K80" t="b">
+        <v>1</v>
+      </c>
+      <c r="L80" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="306" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>237</v>
       </c>
@@ -4113,14 +4621,20 @@
       <c r="F81" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="I81" t="b">
-        <v>0</v>
-      </c>
-      <c r="J81" t="s">
+      <c r="I81" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J81" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K81" t="b">
+        <v>0</v>
+      </c>
+      <c r="L81" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>241</v>
       </c>
@@ -4142,14 +4656,20 @@
       <c r="H82" t="s">
         <v>30</v>
       </c>
-      <c r="I82" t="b">
-        <v>0</v>
-      </c>
-      <c r="J82" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I82" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J82" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K82" t="b">
+        <v>0</v>
+      </c>
+      <c r="L82" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>244</v>
       </c>
@@ -4165,14 +4685,20 @@
       <c r="E83" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="I83" t="b">
-        <v>0</v>
-      </c>
-      <c r="J83" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="I83" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J83" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K83" t="b">
+        <v>0</v>
+      </c>
+      <c r="L83" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>247</v>
       </c>
@@ -4188,14 +4714,20 @@
       <c r="E84" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="I84" t="b">
-        <v>0</v>
-      </c>
-      <c r="J84" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I84" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J84" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K84" t="b">
+        <v>0</v>
+      </c>
+      <c r="L84" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>249</v>
       </c>
@@ -4214,14 +4746,20 @@
       <c r="F85" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="I85" t="b">
-        <v>0</v>
-      </c>
-      <c r="J85" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" ht="289" x14ac:dyDescent="0.2">
+      <c r="I85" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J85" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K85" t="b">
+        <v>0</v>
+      </c>
+      <c r="L85" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="289" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>253</v>
       </c>
@@ -4237,14 +4775,20 @@
       <c r="E86" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="I86" t="b">
-        <v>0</v>
-      </c>
-      <c r="J86" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" ht="372" x14ac:dyDescent="0.2">
+      <c r="I86" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J86" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K86" t="b">
+        <v>0</v>
+      </c>
+      <c r="L86" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="372" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>255</v>
       </c>
@@ -4266,14 +4810,20 @@
       <c r="H87" t="s">
         <v>30</v>
       </c>
-      <c r="I87" t="b">
-        <v>0</v>
-      </c>
-      <c r="J87" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I87" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J87" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K87" t="b">
+        <v>0</v>
+      </c>
+      <c r="L87" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>259</v>
       </c>
@@ -4292,14 +4842,20 @@
       <c r="F88" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="I88" t="b">
-        <v>0</v>
-      </c>
-      <c r="J88" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" ht="204" x14ac:dyDescent="0.2">
+      <c r="I88" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J88" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K88" t="b">
+        <v>0</v>
+      </c>
+      <c r="L88" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" ht="204" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>263</v>
       </c>
@@ -4321,14 +4877,20 @@
       <c r="G89" t="s">
         <v>30</v>
       </c>
-      <c r="I89" t="b">
-        <v>0</v>
-      </c>
-      <c r="J89" t="s">
+      <c r="I89" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J89" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K89" t="b">
+        <v>0</v>
+      </c>
+      <c r="L89" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>267</v>
       </c>
@@ -4347,14 +4909,20 @@
       <c r="H90" t="s">
         <v>30</v>
       </c>
-      <c r="I90" t="b">
-        <v>0</v>
-      </c>
-      <c r="J90" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" ht="372" x14ac:dyDescent="0.2">
+      <c r="I90" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J90" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K90" t="b">
+        <v>0</v>
+      </c>
+      <c r="L90" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="372" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>270</v>
       </c>
@@ -4376,14 +4944,20 @@
       <c r="H91" t="s">
         <v>30</v>
       </c>
-      <c r="I91" t="b">
-        <v>0</v>
-      </c>
-      <c r="J91" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I91" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J91" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K91" t="b">
+        <v>0</v>
+      </c>
+      <c r="L91" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>274</v>
       </c>
@@ -4402,14 +4976,20 @@
       <c r="F92" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="I92" t="b">
-        <v>0</v>
-      </c>
-      <c r="J92" t="s">
+      <c r="I92" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J92" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K92" t="b">
+        <v>0</v>
+      </c>
+      <c r="L92" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>278</v>
       </c>
@@ -4428,14 +5008,20 @@
       <c r="F93" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="I93" t="b">
-        <v>0</v>
-      </c>
-      <c r="J93" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I93" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J93" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K93" t="b">
+        <v>0</v>
+      </c>
+      <c r="L93" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>282</v>
       </c>
@@ -4454,14 +5040,20 @@
       <c r="F94" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="I94" t="b">
-        <v>0</v>
-      </c>
-      <c r="J94" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" ht="372" x14ac:dyDescent="0.2">
+      <c r="I94" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J94" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K94" t="b">
+        <v>0</v>
+      </c>
+      <c r="L94" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="372" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>286</v>
       </c>
@@ -4477,14 +5069,20 @@
       <c r="E95" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="I95" t="b">
-        <v>0</v>
-      </c>
-      <c r="J95" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I95" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J95" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K95" t="b">
+        <v>0</v>
+      </c>
+      <c r="L95" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>288</v>
       </c>
@@ -4500,14 +5098,20 @@
       <c r="E96" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I96" t="b">
-        <v>1</v>
-      </c>
-      <c r="J96" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I96" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J96" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K96" t="b">
+        <v>1</v>
+      </c>
+      <c r="L96" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>290</v>
       </c>
@@ -4529,14 +5133,20 @@
       <c r="H97" t="s">
         <v>30</v>
       </c>
-      <c r="I97" t="b">
-        <v>0</v>
-      </c>
-      <c r="J97" t="s">
+      <c r="I97" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J97" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K97" t="b">
+        <v>0</v>
+      </c>
+      <c r="L97" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>294</v>
       </c>
@@ -4552,14 +5162,20 @@
       <c r="E98" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I98" t="b">
-        <v>1</v>
-      </c>
-      <c r="J98" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I98" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J98" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K98" t="b">
+        <v>1</v>
+      </c>
+      <c r="L98" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>296</v>
       </c>
@@ -4575,14 +5191,20 @@
       <c r="E99" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="I99" t="b">
-        <v>1</v>
-      </c>
-      <c r="J99" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" ht="238" x14ac:dyDescent="0.2">
+      <c r="I99" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J99" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K99" t="b">
+        <v>1</v>
+      </c>
+      <c r="L99" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" ht="238" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>299</v>
       </c>
@@ -4598,14 +5220,20 @@
       <c r="E100" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="I100" t="b">
-        <v>0</v>
-      </c>
-      <c r="J100" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I100" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J100" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K100" t="b">
+        <v>0</v>
+      </c>
+      <c r="L100" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>302</v>
       </c>
@@ -4621,14 +5249,20 @@
       <c r="E101" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I101" t="b">
-        <v>1</v>
-      </c>
-      <c r="J101" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" ht="204" x14ac:dyDescent="0.2">
+      <c r="I101" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J101" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K101" t="b">
+        <v>1</v>
+      </c>
+      <c r="L101" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" ht="204" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>304</v>
       </c>
@@ -4644,14 +5278,20 @@
       <c r="E102" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I102" t="b">
-        <v>1</v>
-      </c>
-      <c r="J102" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I102" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J102" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K102" t="b">
+        <v>1</v>
+      </c>
+      <c r="L102" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>306</v>
       </c>
@@ -4667,14 +5307,20 @@
       <c r="E103" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I103" t="b">
-        <v>1</v>
-      </c>
-      <c r="J103" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I103" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J103" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K103" t="b">
+        <v>1</v>
+      </c>
+      <c r="L103" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>308</v>
       </c>
@@ -4690,14 +5336,20 @@
       <c r="E104" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I104" t="b">
-        <v>1</v>
-      </c>
-      <c r="J104" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+      <c r="I104" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J104" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K104" t="b">
+        <v>1</v>
+      </c>
+      <c r="L104" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" ht="119" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>310</v>
       </c>
@@ -4713,14 +5365,20 @@
       <c r="E105" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I105" t="b">
-        <v>1</v>
-      </c>
-      <c r="J105" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="I105" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J105" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K105" t="b">
+        <v>1</v>
+      </c>
+      <c r="L105" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>312</v>
       </c>
@@ -4736,14 +5394,20 @@
       <c r="E106" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I106" t="b">
-        <v>1</v>
-      </c>
-      <c r="J106" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I106" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J106" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K106" t="b">
+        <v>1</v>
+      </c>
+      <c r="L106" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>314</v>
       </c>
@@ -4759,14 +5423,20 @@
       <c r="E107" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I107" t="b">
-        <v>1</v>
-      </c>
-      <c r="J107" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I107" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J107" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K107" t="b">
+        <v>1</v>
+      </c>
+      <c r="L107" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>316</v>
       </c>
@@ -4788,14 +5458,20 @@
       <c r="H108" t="s">
         <v>30</v>
       </c>
-      <c r="I108" t="b">
-        <v>0</v>
-      </c>
-      <c r="J108" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="I108" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J108" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K108" t="b">
+        <v>0</v>
+      </c>
+      <c r="L108" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" ht="85" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>320</v>
       </c>
@@ -4814,14 +5490,20 @@
       <c r="F109" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="I109" t="b">
-        <v>0</v>
-      </c>
-      <c r="J109" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="I109" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J109" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K109" t="b">
+        <v>0</v>
+      </c>
+      <c r="L109" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>323</v>
       </c>
@@ -4837,14 +5519,20 @@
       <c r="E110" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I110" t="b">
-        <v>1</v>
-      </c>
-      <c r="J110" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="I110" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J110" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K110" t="b">
+        <v>1</v>
+      </c>
+      <c r="L110" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>325</v>
       </c>
@@ -4860,14 +5548,20 @@
       <c r="E111" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I111" t="b">
-        <v>1</v>
-      </c>
-      <c r="J111" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I111" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J111" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K111" t="b">
+        <v>1</v>
+      </c>
+      <c r="L111" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>327</v>
       </c>
@@ -4886,14 +5580,20 @@
       <c r="F112" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="I112" t="b">
-        <v>1</v>
-      </c>
-      <c r="J112" t="s">
+      <c r="I112" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J112" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K112" t="b">
+        <v>1</v>
+      </c>
+      <c r="L112" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="153" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:12" ht="153" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>330</v>
       </c>
@@ -4909,14 +5609,20 @@
       <c r="E113" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I113" t="b">
-        <v>1</v>
-      </c>
-      <c r="J113" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" ht="204" x14ac:dyDescent="0.2">
+      <c r="I113" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J113" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K113" t="b">
+        <v>1</v>
+      </c>
+      <c r="L113" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" ht="204" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>332</v>
       </c>
@@ -4935,14 +5641,20 @@
       <c r="F114" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="I114" t="b">
-        <v>0</v>
-      </c>
-      <c r="J114" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I114" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J114" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K114" t="b">
+        <v>0</v>
+      </c>
+      <c r="L114" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>336</v>
       </c>
@@ -4958,14 +5670,20 @@
       <c r="E115" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I115" t="b">
-        <v>1</v>
-      </c>
-      <c r="J115" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="I115" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J115" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K115" t="b">
+        <v>1</v>
+      </c>
+      <c r="L115" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>338</v>
       </c>
@@ -4981,14 +5699,20 @@
       <c r="E116" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I116" t="b">
-        <v>1</v>
-      </c>
-      <c r="J116" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I116" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J116" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K116" t="b">
+        <v>1</v>
+      </c>
+      <c r="L116" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>340</v>
       </c>
@@ -5004,14 +5728,20 @@
       <c r="E117" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="I117" t="b">
-        <v>1</v>
-      </c>
-      <c r="J117" t="s">
+      <c r="I117" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J117" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K117" t="b">
+        <v>1</v>
+      </c>
+      <c r="L117" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>343</v>
       </c>
@@ -5027,14 +5757,20 @@
       <c r="E118" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I118" t="b">
-        <v>1</v>
-      </c>
-      <c r="J118" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="I118" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J118" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K118" t="b">
+        <v>1</v>
+      </c>
+      <c r="L118" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" ht="68" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>345</v>
       </c>
@@ -5056,14 +5792,20 @@
       <c r="G119" t="s">
         <v>30</v>
       </c>
-      <c r="I119" t="b">
-        <v>0</v>
-      </c>
-      <c r="J119" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I119" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J119" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K119" t="b">
+        <v>0</v>
+      </c>
+      <c r="L119" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>349</v>
       </c>
@@ -5079,14 +5821,20 @@
       <c r="E120" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I120" t="b">
-        <v>1</v>
-      </c>
-      <c r="J120" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" ht="204" x14ac:dyDescent="0.2">
+      <c r="I120" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J120" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K120" t="b">
+        <v>1</v>
+      </c>
+      <c r="L120" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" ht="204" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>351</v>
       </c>
@@ -5108,14 +5856,20 @@
       <c r="H121" t="s">
         <v>30</v>
       </c>
-      <c r="I121" t="b">
-        <v>0</v>
-      </c>
-      <c r="J121" t="s">
+      <c r="I121" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J121" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K121" t="b">
+        <v>0</v>
+      </c>
+      <c r="L121" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>355</v>
       </c>
@@ -5131,14 +5885,20 @@
       <c r="E122" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I122" t="b">
-        <v>1</v>
-      </c>
-      <c r="J122" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I122" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J122" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K122" t="b">
+        <v>1</v>
+      </c>
+      <c r="L122" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>357</v>
       </c>
@@ -5154,14 +5914,20 @@
       <c r="E123" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I123" t="b">
-        <v>1</v>
-      </c>
-      <c r="J123" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="I123" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J123" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K123" t="b">
+        <v>1</v>
+      </c>
+      <c r="L123" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>359</v>
       </c>
@@ -5183,14 +5949,20 @@
       <c r="H124" t="s">
         <v>30</v>
       </c>
-      <c r="I124" t="b">
-        <v>1</v>
-      </c>
-      <c r="J124" t="s">
+      <c r="I124" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J124" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K124" t="b">
+        <v>1</v>
+      </c>
+      <c r="L124" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="187" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:12" ht="187" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>362</v>
       </c>
@@ -5206,14 +5978,20 @@
       <c r="E125" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I125" t="b">
-        <v>0</v>
-      </c>
-      <c r="J125" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I125" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J125" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K125" t="b">
+        <v>0</v>
+      </c>
+      <c r="L125" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>364</v>
       </c>
@@ -5229,14 +6007,20 @@
       <c r="E126" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I126" t="b">
-        <v>1</v>
-      </c>
-      <c r="J126" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I126" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J126" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K126" t="b">
+        <v>1</v>
+      </c>
+      <c r="L126" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>366</v>
       </c>
@@ -5252,14 +6036,20 @@
       <c r="E127" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I127" t="b">
-        <v>1</v>
-      </c>
-      <c r="J127" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I127" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J127" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K127" t="b">
+        <v>1</v>
+      </c>
+      <c r="L127" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>368</v>
       </c>
@@ -5278,14 +6068,20 @@
       <c r="F128" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="I128" t="b">
-        <v>1</v>
-      </c>
-      <c r="J128" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10" ht="221" x14ac:dyDescent="0.2">
+      <c r="I128" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J128" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K128" t="b">
+        <v>1</v>
+      </c>
+      <c r="L128" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" ht="221" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>372</v>
       </c>
@@ -5307,14 +6103,20 @@
       <c r="H129" t="s">
         <v>30</v>
       </c>
-      <c r="I129" t="b">
-        <v>0</v>
-      </c>
-      <c r="J129" t="s">
+      <c r="I129" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J129" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K129" t="b">
+        <v>0</v>
+      </c>
+      <c r="L129" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>376</v>
       </c>
@@ -5330,14 +6132,20 @@
       <c r="E130" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="I130" t="b">
-        <v>0</v>
-      </c>
-      <c r="J130" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I130" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J130" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K130" t="b">
+        <v>0</v>
+      </c>
+      <c r="L130" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>379</v>
       </c>
@@ -5353,14 +6161,20 @@
       <c r="E131" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I131" t="b">
-        <v>1</v>
-      </c>
-      <c r="J131" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I131" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J131" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K131" t="b">
+        <v>1</v>
+      </c>
+      <c r="L131" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>381</v>
       </c>
@@ -5376,14 +6190,20 @@
       <c r="E132" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="I132" t="b">
-        <v>0</v>
-      </c>
-      <c r="J132" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I132" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J132" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K132" t="b">
+        <v>0</v>
+      </c>
+      <c r="L132" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>384</v>
       </c>
@@ -5399,14 +6219,20 @@
       <c r="E133" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I133" t="b">
-        <v>1</v>
-      </c>
-      <c r="J133" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="I133" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J133" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K133" t="b">
+        <v>1</v>
+      </c>
+      <c r="L133" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>386</v>
       </c>
@@ -5422,14 +6248,20 @@
       <c r="E134" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I134" t="b">
-        <v>1</v>
-      </c>
-      <c r="J134" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I134" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J134" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K134" t="b">
+        <v>1</v>
+      </c>
+      <c r="L134" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>388</v>
       </c>
@@ -5445,14 +6277,20 @@
       <c r="E135" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I135" t="b">
-        <v>1</v>
-      </c>
-      <c r="J135" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I135" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J135" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K135" t="b">
+        <v>1</v>
+      </c>
+      <c r="L135" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>390</v>
       </c>
@@ -5468,14 +6306,20 @@
       <c r="E136" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="I136" t="b">
-        <v>0</v>
-      </c>
-      <c r="J136" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I136" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J136" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K136" t="b">
+        <v>0</v>
+      </c>
+      <c r="L136" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>393</v>
       </c>
@@ -5491,14 +6335,20 @@
       <c r="E137" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I137" t="b">
-        <v>1</v>
-      </c>
-      <c r="J137" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I137" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J137" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K137" t="b">
+        <v>1</v>
+      </c>
+      <c r="L137" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>395</v>
       </c>
@@ -5514,14 +6364,20 @@
       <c r="E138" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I138" t="b">
-        <v>1</v>
-      </c>
-      <c r="J138" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I138" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J138" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K138" t="b">
+        <v>1</v>
+      </c>
+      <c r="L138" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>397</v>
       </c>
@@ -5540,14 +6396,20 @@
       <c r="F139" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="I139" t="b">
-        <v>0</v>
-      </c>
-      <c r="J139" t="s">
+      <c r="I139" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J139" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K139" t="b">
+        <v>0</v>
+      </c>
+      <c r="L139" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="170" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:12" ht="170" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>401</v>
       </c>
@@ -5569,14 +6431,20 @@
       <c r="H140" t="s">
         <v>30</v>
       </c>
-      <c r="I140" t="b">
-        <v>0</v>
-      </c>
-      <c r="J140" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I140" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J140" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K140" t="b">
+        <v>0</v>
+      </c>
+      <c r="L140" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>404</v>
       </c>
@@ -5595,14 +6463,20 @@
       <c r="F141" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="I141" t="b">
-        <v>0</v>
-      </c>
-      <c r="J141" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="I141" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J141" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K141" t="b">
+        <v>0</v>
+      </c>
+      <c r="L141" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>408</v>
       </c>
@@ -5618,14 +6492,20 @@
       <c r="E142" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I142" t="b">
-        <v>1</v>
-      </c>
-      <c r="J142" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" ht="221" x14ac:dyDescent="0.2">
+      <c r="I142" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J142" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K142" t="b">
+        <v>1</v>
+      </c>
+      <c r="L142" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" ht="221" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>410</v>
       </c>
@@ -5644,14 +6524,20 @@
       <c r="F143" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="I143" t="b">
-        <v>0</v>
-      </c>
-      <c r="J143" t="s">
+      <c r="I143" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J143" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K143" t="b">
+        <v>0</v>
+      </c>
+      <c r="L143" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="255" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:12" ht="255" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>414</v>
       </c>
@@ -5673,14 +6559,20 @@
       <c r="H144" t="s">
         <v>30</v>
       </c>
-      <c r="I144" t="b">
-        <v>0</v>
-      </c>
-      <c r="J144" t="s">
+      <c r="I144" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J144" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K144" t="b">
+        <v>0</v>
+      </c>
+      <c r="L144" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>418</v>
       </c>
@@ -5702,14 +6594,20 @@
       <c r="H145" t="s">
         <v>30</v>
       </c>
-      <c r="I145" t="b">
-        <v>0</v>
-      </c>
-      <c r="J145" t="s">
+      <c r="I145" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J145" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K145" t="b">
+        <v>0</v>
+      </c>
+      <c r="L145" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>421</v>
       </c>
@@ -5725,14 +6623,20 @@
       <c r="E146" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I146" t="b">
-        <v>1</v>
-      </c>
-      <c r="J146" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="147" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I146" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J146" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K146" t="b">
+        <v>1</v>
+      </c>
+      <c r="L146" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>423</v>
       </c>
@@ -5748,14 +6652,20 @@
       <c r="E147" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I147" t="b">
-        <v>1</v>
-      </c>
-      <c r="J147" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="148" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I147" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J147" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K147" t="b">
+        <v>1</v>
+      </c>
+      <c r="L147" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>425</v>
       </c>
@@ -5771,14 +6681,20 @@
       <c r="E148" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I148" t="b">
-        <v>1</v>
-      </c>
-      <c r="J148" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="149" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I148" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J148" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K148" t="b">
+        <v>1</v>
+      </c>
+      <c r="L148" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>427</v>
       </c>
@@ -5794,14 +6710,20 @@
       <c r="E149" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I149" t="b">
-        <v>1</v>
-      </c>
-      <c r="J149" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="150" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="I149" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J149" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K149" t="b">
+        <v>1</v>
+      </c>
+      <c r="L149" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>429</v>
       </c>
@@ -5817,14 +6739,20 @@
       <c r="E150" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I150" t="b">
-        <v>1</v>
-      </c>
-      <c r="J150" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="151" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I150" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J150" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K150" t="b">
+        <v>1</v>
+      </c>
+      <c r="L150" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>431</v>
       </c>
@@ -5840,14 +6768,20 @@
       <c r="E151" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I151" t="b">
-        <v>1</v>
-      </c>
-      <c r="J151" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="152" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I151" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J151" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K151" t="b">
+        <v>1</v>
+      </c>
+      <c r="L151" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>433</v>
       </c>
@@ -5863,14 +6797,20 @@
       <c r="E152" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I152" t="b">
-        <v>1</v>
-      </c>
-      <c r="J152" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="I152" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J152" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K152" t="b">
+        <v>1</v>
+      </c>
+      <c r="L152" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" ht="85" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>435</v>
       </c>
@@ -5895,14 +6835,20 @@
       <c r="H153" t="s">
         <v>30</v>
       </c>
-      <c r="I153" t="b">
-        <v>0</v>
-      </c>
-      <c r="J153" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="154" spans="1:10" ht="272" x14ac:dyDescent="0.2">
+      <c r="I153" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J153" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K153" t="b">
+        <v>0</v>
+      </c>
+      <c r="L153" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" ht="272" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>439</v>
       </c>
@@ -5918,14 +6864,20 @@
       <c r="E154" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="I154" t="b">
-        <v>0</v>
-      </c>
-      <c r="J154" t="s">
+      <c r="I154" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J154" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K154" t="b">
+        <v>0</v>
+      </c>
+      <c r="L154" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="155" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>442</v>
       </c>
@@ -5941,14 +6893,20 @@
       <c r="E155" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I155" t="b">
-        <v>1</v>
-      </c>
-      <c r="J155" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="156" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I155" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J155" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K155" t="b">
+        <v>1</v>
+      </c>
+      <c r="L155" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>444</v>
       </c>
@@ -5964,14 +6922,20 @@
       <c r="E156" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I156" t="b">
-        <v>1</v>
-      </c>
-      <c r="J156" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="157" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="I156" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J156" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K156" t="b">
+        <v>1</v>
+      </c>
+      <c r="L156" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>446</v>
       </c>
@@ -5987,14 +6951,20 @@
       <c r="E157" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I157" t="b">
-        <v>1</v>
-      </c>
-      <c r="J157" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="158" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I157" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J157" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K157" t="b">
+        <v>1</v>
+      </c>
+      <c r="L157" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>448</v>
       </c>
@@ -6010,14 +6980,20 @@
       <c r="E158" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="I158" t="b">
-        <v>0</v>
-      </c>
-      <c r="J158" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="159" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I158" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J158" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K158" t="b">
+        <v>0</v>
+      </c>
+      <c r="L158" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>450</v>
       </c>
@@ -6033,14 +7009,20 @@
       <c r="E159" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="I159" t="b">
-        <v>0</v>
-      </c>
-      <c r="J159" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="160" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I159" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J159" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K159" t="b">
+        <v>0</v>
+      </c>
+      <c r="L159" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>453</v>
       </c>
@@ -6056,14 +7038,20 @@
       <c r="E160" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I160" t="b">
-        <v>1</v>
-      </c>
-      <c r="J160" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="161" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I160" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J160" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K160" t="b">
+        <v>1</v>
+      </c>
+      <c r="L160" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>455</v>
       </c>
@@ -6085,14 +7073,20 @@
       <c r="H161" t="s">
         <v>30</v>
       </c>
-      <c r="I161" t="b">
-        <v>0</v>
-      </c>
-      <c r="J161" t="s">
+      <c r="I161" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J161" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K161" t="b">
+        <v>0</v>
+      </c>
+      <c r="L161" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="162" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>459</v>
       </c>
@@ -6108,14 +7102,20 @@
       <c r="E162" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I162" t="b">
-        <v>1</v>
-      </c>
-      <c r="J162" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="163" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I162" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J162" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K162" t="b">
+        <v>1</v>
+      </c>
+      <c r="L162" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>461</v>
       </c>
@@ -6131,14 +7131,20 @@
       <c r="E163" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I163" t="b">
-        <v>1</v>
-      </c>
-      <c r="J163" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="164" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="I163" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J163" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K163" t="b">
+        <v>1</v>
+      </c>
+      <c r="L163" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" ht="85" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>463</v>
       </c>
@@ -6154,14 +7160,20 @@
       <c r="E164" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I164" t="b">
-        <v>1</v>
-      </c>
-      <c r="J164" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="165" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="I164" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J164" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K164" t="b">
+        <v>1</v>
+      </c>
+      <c r="L164" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>465</v>
       </c>
@@ -6180,14 +7192,20 @@
       <c r="F165" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="I165" t="b">
-        <v>1</v>
-      </c>
-      <c r="J165" t="s">
+      <c r="I165" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J165" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K165" t="b">
+        <v>1</v>
+      </c>
+      <c r="L165" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="166" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>468</v>
       </c>
@@ -6203,14 +7221,20 @@
       <c r="E166" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I166" t="b">
-        <v>1</v>
-      </c>
-      <c r="J166" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="167" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="I166" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J166" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K166" t="b">
+        <v>1</v>
+      </c>
+      <c r="L166" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>470</v>
       </c>
@@ -6226,14 +7250,20 @@
       <c r="E167" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I167" t="b">
-        <v>1</v>
-      </c>
-      <c r="J167" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="168" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I167" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J167" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K167" t="b">
+        <v>1</v>
+      </c>
+      <c r="L167" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>472</v>
       </c>
@@ -6249,14 +7279,20 @@
       <c r="E168" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I168" t="b">
-        <v>1</v>
-      </c>
-      <c r="J168" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="169" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I168" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J168" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K168" t="b">
+        <v>1</v>
+      </c>
+      <c r="L168" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>474</v>
       </c>
@@ -6272,14 +7308,20 @@
       <c r="E169" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="I169" t="b">
-        <v>0</v>
-      </c>
-      <c r="J169" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="170" spans="1:10" ht="289" x14ac:dyDescent="0.2">
+      <c r="I169" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J169" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K169" t="b">
+        <v>0</v>
+      </c>
+      <c r="L169" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" ht="289" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>477</v>
       </c>
@@ -6295,14 +7337,20 @@
       <c r="E170" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="I170" t="b">
-        <v>0</v>
-      </c>
-      <c r="J170" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="171" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I170" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J170" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K170" t="b">
+        <v>0</v>
+      </c>
+      <c r="L170" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>480</v>
       </c>
@@ -6318,14 +7366,20 @@
       <c r="E171" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I171" t="b">
-        <v>1</v>
-      </c>
-      <c r="J171" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="172" spans="1:10" ht="187" x14ac:dyDescent="0.2">
+      <c r="I171" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J171" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K171" t="b">
+        <v>1</v>
+      </c>
+      <c r="L171" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" ht="187" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>482</v>
       </c>
@@ -6344,14 +7398,20 @@
       <c r="F172" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="I172" t="b">
-        <v>0</v>
-      </c>
-      <c r="J172" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="173" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I172" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J172" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K172" t="b">
+        <v>0</v>
+      </c>
+      <c r="L172" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>485</v>
       </c>
@@ -6367,14 +7427,20 @@
       <c r="F173" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="I173" t="b">
-        <v>0</v>
-      </c>
-      <c r="J173" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="174" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I173" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J173" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K173" t="b">
+        <v>0</v>
+      </c>
+      <c r="L173" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>488</v>
       </c>
@@ -6390,14 +7456,20 @@
       <c r="E174" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I174" t="b">
-        <v>1</v>
-      </c>
-      <c r="J174" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="175" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I174" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J174" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K174" t="b">
+        <v>1</v>
+      </c>
+      <c r="L174" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>490</v>
       </c>
@@ -6413,14 +7485,20 @@
       <c r="E175" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="I175" t="b">
-        <v>1</v>
-      </c>
-      <c r="J175" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="176" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I175" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J175" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K175" t="b">
+        <v>1</v>
+      </c>
+      <c r="L175" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>493</v>
       </c>
@@ -6436,14 +7514,20 @@
       <c r="E176" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I176" t="b">
-        <v>1</v>
-      </c>
-      <c r="J176" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="177" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I176" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J176" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K176" t="b">
+        <v>1</v>
+      </c>
+      <c r="L176" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>495</v>
       </c>
@@ -6459,14 +7543,20 @@
       <c r="E177" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I177" t="b">
-        <v>1</v>
-      </c>
-      <c r="J177" t="s">
+      <c r="I177" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J177" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K177" t="b">
+        <v>1</v>
+      </c>
+      <c r="L177" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="178" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>497</v>
       </c>
@@ -6485,14 +7575,20 @@
       <c r="H178" t="s">
         <v>30</v>
       </c>
-      <c r="I178" t="b">
-        <v>0</v>
-      </c>
-      <c r="J178" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="179" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="I178" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J178" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K178" t="b">
+        <v>0</v>
+      </c>
+      <c r="L178" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>500</v>
       </c>
@@ -6508,14 +7604,20 @@
       <c r="E179" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I179" t="b">
-        <v>1</v>
-      </c>
-      <c r="J179" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="180" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+      <c r="I179" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J179" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K179" t="b">
+        <v>1</v>
+      </c>
+      <c r="L179" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" ht="119" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>502</v>
       </c>
@@ -6534,14 +7636,20 @@
       <c r="F180" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="I180" t="b">
-        <v>0</v>
-      </c>
-      <c r="J180" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="181" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="I180" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J180" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K180" t="b">
+        <v>0</v>
+      </c>
+      <c r="L180" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>506</v>
       </c>
@@ -6557,14 +7665,20 @@
       <c r="E181" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I181" t="b">
-        <v>1</v>
-      </c>
-      <c r="J181" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="182" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="I181" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J181" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K181" t="b">
+        <v>1</v>
+      </c>
+      <c r="L181" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" ht="85" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>508</v>
       </c>
@@ -6580,14 +7694,20 @@
       <c r="E182" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="I182" t="b">
-        <v>0</v>
-      </c>
-      <c r="J182" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="183" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I182" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J182" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K182" t="b">
+        <v>0</v>
+      </c>
+      <c r="L182" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>510</v>
       </c>
@@ -6603,14 +7723,20 @@
       <c r="E183" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I183" t="b">
-        <v>1</v>
-      </c>
-      <c r="J183" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="184" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I183" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J183" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K183" t="b">
+        <v>1</v>
+      </c>
+      <c r="L183" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A184" s="2" t="s">
         <v>512</v>
       </c>
@@ -6633,14 +7759,20 @@
       <c r="H184" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="I184" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J184" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="185" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I184" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J184" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K184" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L184" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>516</v>
       </c>
@@ -6656,14 +7788,20 @@
       <c r="E185" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I185" t="b">
-        <v>1</v>
-      </c>
-      <c r="J185" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="186" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I185" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J185" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K185" t="b">
+        <v>1</v>
+      </c>
+      <c r="L185" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>518</v>
       </c>
@@ -6679,14 +7817,20 @@
       <c r="E186" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I186" t="b">
-        <v>1</v>
-      </c>
-      <c r="J186" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="187" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I186" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J186" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K186" t="b">
+        <v>1</v>
+      </c>
+      <c r="L186" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>520</v>
       </c>
@@ -6705,14 +7849,20 @@
       <c r="F187" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="I187" t="b">
-        <v>0</v>
-      </c>
-      <c r="J187" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="188" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I187" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J187" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K187" t="b">
+        <v>0</v>
+      </c>
+      <c r="L187" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>523</v>
       </c>
@@ -6728,14 +7878,20 @@
       <c r="E188" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="I188" t="b">
-        <v>0</v>
-      </c>
-      <c r="J188" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="189" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I188" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J188" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K188" t="b">
+        <v>0</v>
+      </c>
+      <c r="L188" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>526</v>
       </c>
@@ -6757,14 +7913,20 @@
       <c r="H189" t="s">
         <v>30</v>
       </c>
-      <c r="I189" t="b">
-        <v>0</v>
-      </c>
-      <c r="J189" t="s">
+      <c r="I189" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J189" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K189" t="b">
+        <v>0</v>
+      </c>
+      <c r="L189" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="190" spans="1:10" ht="289" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:12" ht="289" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>530</v>
       </c>
@@ -6783,14 +7945,20 @@
       <c r="G190" t="s">
         <v>30</v>
       </c>
-      <c r="I190" t="b">
-        <v>0</v>
-      </c>
-      <c r="J190" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="191" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I190" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J190" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K190" t="b">
+        <v>0</v>
+      </c>
+      <c r="L190" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>533</v>
       </c>
@@ -6806,14 +7974,20 @@
       <c r="E191" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I191" t="b">
-        <v>1</v>
-      </c>
-      <c r="J191" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="192" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="I191" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J191" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K191" t="b">
+        <v>1</v>
+      </c>
+      <c r="L191" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>535</v>
       </c>
@@ -6832,14 +8006,20 @@
       <c r="F192" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="I192" t="b">
-        <v>0</v>
-      </c>
-      <c r="J192" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="193" spans="1:10" ht="204" x14ac:dyDescent="0.2">
+      <c r="I192" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J192" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K192" t="b">
+        <v>0</v>
+      </c>
+      <c r="L192" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12" ht="204" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>538</v>
       </c>
@@ -6858,14 +8038,20 @@
       <c r="F193" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="I193" t="b">
-        <v>0</v>
-      </c>
-      <c r="J193" t="s">
+      <c r="I193" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J193" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K193" t="b">
+        <v>0</v>
+      </c>
+      <c r="L193" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="194" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>541</v>
       </c>
@@ -6881,14 +8067,20 @@
       <c r="E194" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I194" t="b">
-        <v>1</v>
-      </c>
-      <c r="J194" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="195" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I194" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J194" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K194" t="b">
+        <v>1</v>
+      </c>
+      <c r="L194" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>543</v>
       </c>
@@ -6904,14 +8096,20 @@
       <c r="E195" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I195" t="b">
-        <v>1</v>
-      </c>
-      <c r="J195" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="196" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="I195" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J195" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K195" t="b">
+        <v>1</v>
+      </c>
+      <c r="L195" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>545</v>
       </c>
@@ -6927,14 +8125,20 @@
       <c r="E196" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I196" t="b">
-        <v>1</v>
-      </c>
-      <c r="J196" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="197" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I196" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J196" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K196" t="b">
+        <v>1</v>
+      </c>
+      <c r="L196" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="197" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>547</v>
       </c>
@@ -6956,14 +8160,20 @@
       <c r="G197" t="s">
         <v>30</v>
       </c>
-      <c r="I197" t="b">
-        <v>0</v>
-      </c>
-      <c r="J197" t="s">
+      <c r="I197" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J197" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K197" t="b">
+        <v>0</v>
+      </c>
+      <c r="L197" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="198" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>551</v>
       </c>
@@ -6979,14 +8189,20 @@
       <c r="E198" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="I198" t="b">
-        <v>0</v>
-      </c>
-      <c r="J198" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="199" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I198" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J198" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K198" t="b">
+        <v>0</v>
+      </c>
+      <c r="L198" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="199" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>554</v>
       </c>
@@ -7002,14 +8218,20 @@
       <c r="E199" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I199" t="b">
-        <v>1</v>
-      </c>
-      <c r="J199" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="200" spans="1:10" ht="204" x14ac:dyDescent="0.2">
+      <c r="I199" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J199" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K199" t="b">
+        <v>1</v>
+      </c>
+      <c r="L199" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12" ht="204" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>556</v>
       </c>
@@ -7025,14 +8247,20 @@
       <c r="E200" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="I200" t="b">
-        <v>0</v>
-      </c>
-      <c r="J200" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="201" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I200" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J200" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K200" t="b">
+        <v>0</v>
+      </c>
+      <c r="L200" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>559</v>
       </c>
@@ -7045,10 +8273,16 @@
       <c r="D201" t="s">
         <v>12</v>
       </c>
-      <c r="I201" t="b">
-        <v>1</v>
-      </c>
-      <c r="J201" t="s">
+      <c r="I201" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J201" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="K201" t="b">
+        <v>1</v>
+      </c>
+      <c r="L201" t="s">
         <v>12</v>
       </c>
     </row>
